--- a/output_boron/boron_Intermediate_bartoli_2011.xlsx
+++ b/output_boron/boron_Intermediate_bartoli_2011.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1029/2010PA002055</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_bartoli_2011.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_bartoli_2011_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">LR04 benthic oxygen isotope stack: L. E. Lisiecki, M. E. Raymo, Paleoceanography 20, 10.1029/2004PA001071 (2005)</t>
+    <t xml:space="preserve">LR04 benthic oxygen isotope stack: L. E. Lisiecki, M. E. Raymo, Paleoceanography 20, 10.1029/2004PA001071 (2005), including uncertainty estimates</t>
   </si>
   <si>
     <t xml:space="preserve">Globigerinoides saculifer</t>
@@ -1527,7 +1527,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1587,12 +1587,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1706,7 +1700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1788,7 +1782,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2395,7 +2388,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2472,7 +2465,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2549,7 +2542,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2626,7 +2619,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2703,7 +2696,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2780,7 +2773,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2857,7 +2850,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2934,7 +2927,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -3011,7 +3004,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3088,7 +3081,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3165,7 +3158,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3242,7 +3235,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3319,7 +3312,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3396,7 +3389,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3473,7 +3466,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3550,7 +3543,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3627,7 +3620,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3704,7 +3697,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3781,7 +3774,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3858,7 +3851,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3935,7 +3928,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -4012,7 +4005,7 @@
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4089,7 +4082,7 @@
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4166,7 +4159,7 @@
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4243,7 +4236,7 @@
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4320,7 +4313,7 @@
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4397,7 +4390,7 @@
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4474,7 +4467,7 @@
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4551,7 +4544,7 @@
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4628,7 +4621,7 @@
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4705,7 +4698,7 @@
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4782,7 +4775,7 @@
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4859,7 +4852,7 @@
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -4936,7 +4929,7 @@
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -5013,7 +5006,7 @@
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5090,7 +5083,7 @@
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5167,7 +5160,7 @@
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5244,7 +5237,7 @@
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5321,7 +5314,7 @@
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5398,7 +5391,7 @@
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5475,7 +5468,7 @@
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5552,7 +5545,7 @@
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5808,50 +5801,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
